--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Full-Stack)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eLink Design</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,69 +486,69 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python</t>
+          <t>RAG, TensorFlow, MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Seaborn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284ca0ae0026bd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer (React UI) - Remote US</t>
+          <t>GenAI Engineer | Washington, DC | Job # 5139</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cielo</t>
+          <t>Accenture Federal Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wauwatosa, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e67add270aac4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b26ab2609fca8f7e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SENIOR DATA ANALYST / TABLEAU DEVELOPER</t>
+          <t>DevOps and Software Lab Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Data and Analytic Solutions, Inc.</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, Redshift, Tableau, Quicksight, MicroStrategy, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592957d84c7c4f25</t>
+          <t>https://www.indeed.com/viewjob?jk=bc42b99c26c9b761</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer - Mobile</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Protiviti</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, PyTorch, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, SQL, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,77 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=286720047d49b635</t>
+          <t>https://www.indeed.com/viewjob?jk=b79c0f2cf017e775</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Mobile</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, SQL, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2823e0104c70eef8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Algorithm Developer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ae7d87b3840a5f0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Duetto Research</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Seaborn</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=39c3deaa7a8471b3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Engineer | Washington, DC | Job # 5139</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Accenture Federal Services</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, FAISS, Pinecone, ChromaDB, Prompt Engineering, Docker</t>
+          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b26ab2609fca8f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps and Software Lab Engineer</t>
+          <t>Software Engineer (Mid-Senior) - Multiple Openings</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Better Planet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, FastAPI, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc42b99c26c9b761</t>
+          <t>https://www.indeed.com/viewjob?jk=73416cf86e21464a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Mobile</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, SQL, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b79c0f2cf017e775</t>
+          <t>https://www.indeed.com/viewjob?jk=5afa505414f90384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Mobile</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, SQL, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2823e0104c70eef8</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AI Algorithm Developer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Applied Materials</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ae7d87b3840a5f0</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duetto Research</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c3deaa7a8471b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, PySpark, Kafka, Python, SQL, R</t>
+          <t>Gemini, GCP Vertex AI, BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer (Mid-Senior) - Multiple Openings</t>
+          <t>AI and Machine Learning Intern (May-Aug '26)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Better Planet</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, Git, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73416cf86e21464a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c90f90963ae9ee6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Alphanumeric Systems Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Scala</t>
+          <t>RAG, Synapse, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afa505414f90384</t>
+          <t>https://www.indeed.com/viewjob?jk=7dfccdbdeb3334ea</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>RZR Global Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=04ec2f769f209544</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Specialist</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e284c7fddcc12ecd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gemini, GCP Vertex AI, BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning Intern (May-Aug '26)</t>
+          <t>AI Engineer-Machine Learning Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c90f90963ae9ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer*</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alphanumeric Systems Inc</t>
+          <t>Meltwater</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,322 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dfccdbdeb3334ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2f03d705cce6cfba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RZR Global Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, SQL, R</t>
+          <t>Copilot, CI/CD, Jenkins, Git, PostgreSQL, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ec2f769f209544</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f6cec85f15b4bd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Talent Acquisition Specialist</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Redshift, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intern, Data Scientist - Summer 2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AriensCo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brillion, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03325f9b0c180932</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>United Vein &amp; Vascular Centers</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior GenAI Engineer - Solutions Architecture</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4e69cf401185863</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT Business Applications Analyst II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Millennium Physician Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fort Myers, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, Cortex, TensorFlow, PyTorch, Athena, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8b53ee73f023245</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Python Engineer - Technical Research &amp; Development</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a2357cec8e9c0c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>National Carwash Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e284c7fddcc12ecd</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ae8d897b256b954</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer - Global Commercial Services Technology</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d44fb29aa5a985</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer-Machine Learning Platform</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac07d11154ac5713</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer*</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meltwater</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Kubernetes, CI/CD, Terraform, Kafka, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f03d705cce6cfba</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Jenkins, Git, PostgreSQL, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f6cec85f15b4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Redshift, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Intern, Data Scientist - Summer 2026</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AriensCo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brillion, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03325f9b0c180932</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=da1a89fff844c24c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior GenAI Engineer - Solutions Architecture</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Pulsora</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e69cf401185863</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8e2f18a0bdf37f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Business Applications Analyst II</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Millennium Physician Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Cortex, TensorFlow, PyTorch, Athena, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b53ee73f023245</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Python Engineer - Technical Research &amp; Development</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Git, Python, R</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Tableau, Power BI, MicroStrategy, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2357cec8e9c0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>National Carwash Solutions, Inc.</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, BigQuery, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,497 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae8d897b256b954</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Global Commercial Services Technology</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c77c644ce82fffe</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc736ea1ce434363</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a3fbd0f9ffcb06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586acdf51b4e1375</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer (RAG Specialist)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NexOne, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Clearfield, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=098c6b6089044845</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Frontend</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d4b89d9018c7b74</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, PySpark, Tableau, Power BI, MicroStrategy, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc324f83a672f133</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer - USC/GC/GC-EAD || W2 Role</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=841078a10e8fdb55</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior EKS Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CG Infinity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=259a39ba6c67b07b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist, People &amp; Workforce Analytics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ivy Rehab Network</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3b34177c717e438</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Pinecone, TensorFlow, Keras, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=addab02fd093dde7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d44fb29aa5a985</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45f46a050f1b2f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Traba</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44a8c350b3c29695</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Red Teamer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HiddenLayer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bffe5b38256073b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>RAG, S3, Glue, BigQuery, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Technical Client Delivery Specialist - Source AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab5c5578b7f0325</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1213ab94fde3b7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=485570cd75c5ce0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Associate AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=20331e1ecc883f27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=9b713cd29943c527</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=2131a2b0afb396af</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Kubernetes, Terraform, Git</t>
+          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1a89fff844c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=5998a562e5789f38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist - Hybrid</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pulsora</t>
+          <t>National Interstate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richfield, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Git, Python</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8e2f18a0bdf37f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2de3178a08fc3d6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cooley LLP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Python, SQL, R</t>
+          <t>RAG, AWS SageMaker, S3, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e395196621404cc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Tableau, Power BI, MicroStrategy, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,532 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GCP Data Cloud Architect with AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FreshDirect</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Woodbridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, BigQuery, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c77c644ce82fffe</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc736ea1ce434363</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Traba</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a3fbd0f9ffcb06</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Traba</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=586acdf51b4e1375</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Engineer (RAG Specialist)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NexOne, Inc.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Clearfield, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=098c6b6089044845</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Frontend</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Lennar</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d4b89d9018c7b74</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NBCUniversal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Snowflake, Databricks, PySpark, Tableau, Power BI, MicroStrategy, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc324f83a672f133</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer - USC/GC/GC-EAD || W2 Role</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Hudson Manpower</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=841078a10e8fdb55</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior EKS Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CG Infinity</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=259a39ba6c67b07b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist, People &amp; Workforce Analytics</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ivy Rehab Network</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Power BI, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b34177c717e438</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lennar</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Pinecone, TensorFlow, Keras, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=addab02fd093dde7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f45f46a050f1b2f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Traba</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44a8c350b3c29695</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Red Teamer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>HiddenLayer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Keras, Python, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bffe5b38256073b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf2f37d89ad7135c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, BigQuery, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Client Delivery Specialist - Source AI</t>
+          <t>Senior LLM Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Viva Capital Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Data Lake, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab5c5578b7f0325</t>
+          <t>https://www.indeed.com/viewjob?jk=4ace6fc421e95558</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1213ab94fde3b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>AI Support Engineer (II+)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485570cd75c5ce0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5eaa8abc9f40633</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate AI Engineer</t>
+          <t>AI Support Engineer (II+)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20331e1ecc883f27</t>
+          <t>https://www.indeed.com/viewjob?jk=73e4cc34b1904e61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Well Dot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chapel Hill, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, LLaMA, Prompt Engineering, Kinesis, CI/CD, Terraform, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b713cd29943c527</t>
+          <t>https://www.indeed.com/viewjob?jk=86857645539bda0f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2131a2b0afb396af</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Terraform, Git, Snowflake, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5998a562e5789f38</t>
+          <t>https://www.indeed.com/viewjob?jk=bae54bff3eb643fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist - Hybrid</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Interstate</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richfield, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2de3178a08fc3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooley LLP</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, S3, Glue, Athena, Data Lake, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,532 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e395196621404cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Data Engineer - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ba4a8f80cd2e4b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, XGBoost, CI/CD, Snowflake, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e269aba562e9a51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Junior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SynapseMX, Inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb1e2deecc1d177</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wrench.ai Inc</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fef37ce9e0766b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NIKE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Docker, AKS, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8cf83aa3a785af4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16d062366902d4af</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SynapseMX, Inc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Docker, Terraform, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f393943987fdc8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mid-Level Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SynapseMX, Inc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98b3ac139c0ec2c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Analytics Engineer III</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sovos</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, Tableau, Quicksight, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fb9cef50f08db1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S3, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e692a5cc45150845</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, NLP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Datavant</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2f37d89ad7135c</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51d70050e888e960</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Oracle PeopleSoft DBA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Data Lake, Git, MySQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c3a991ee93a8420</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Security Engineer - Dallas - Associate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Git, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6f0853676829ed4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cushman &amp; Wakefield</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Creve Coeur, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4b21e6d09fdd6f1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-20.xlsx
+++ b/daily_matches/job_matches_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior LLM Developer</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Viva Capital Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Data Lake, FastAPI, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ace6fc421e95558</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6c9a9373ca32f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Software Development Engineer 3, Resi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Pushpay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Generative AI, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef546f6f6a7e7d20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Support Engineer (II+)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
+          <t>Data Scientist, RAG, S3, Docker, Git, Snowflake, Databricks, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5eaa8abc9f40633</t>
+          <t>https://www.indeed.com/viewjob?jk=a40eac651546185e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Support Engineer (II+)</t>
+          <t>Senior Software Architect- Enterprise Systems</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Toshiba Global Commerce Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e4cc34b1904e61</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5000b9ca16b3c5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Capital Insights</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Well Dot</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, LLaMA, Prompt Engineering, Kinesis, CI/CD, Terraform, PostgreSQL, SQL</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86857645539bda0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c4a24d39ecba29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Known</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Terraform, Git, Snowflake, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae54bff3eb643fb</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Snowflake, Databricks, BigQuery, Tableau, Python, SQL</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Glue, Athena, Data Lake, Snowflake, Databricks, Python, SQL</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Supply Chain</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba4a8f80cd2e4b2</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist - Supply Chain</t>
+          <t>Data Scientist - Production Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Cordial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, XGBoost, CI/CD, Snowflake, Databricks, Python, SQL</t>
+          <t>Data Scientist, S3, Glue, Athena, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e269aba562e9a51</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8e2cc9e6cd3e4a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior Full-Stack Software Engineer</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SynapseMX, Inc</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>RAG, Prompt Engineering, Cortex, Docker, Kubernetes, CI/CD, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb1e2deecc1d177</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Machine Learning Infrastructure Engineer, GenAI Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wrench.ai Inc</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef37ce9e0766b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f54931a90db4be</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT AI Innovation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Holland &amp; Knight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Brandon, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Java</t>
+          <t>RAG, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=f120a08f681fa24f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Data Engineer III - Python / AWS / SQL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, AKS, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cf83aa3a785af4</t>
+          <t>https://www.indeed.com/viewjob?jk=47737cefdf9cb799</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Supply Chain</t>
+          <t>Senior Forward Deployed Engineer - SnowConvert AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,287 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d062366902d4af</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SynapseMX, Inc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Docker, Terraform, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f393943987fdc8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mid-Level Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SynapseMX, Inc</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Docker, Kubernetes, Terraform, Git, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98b3ac139c0ec2c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Analytics Engineer III</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sovos</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Tableau, Quicksight, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fb9cef50f08db1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>S3, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e692a5cc45150845</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, NLP</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Datavant</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d70050e888e960</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Oracle PeopleSoft DBA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Data Lake, Git, MySQL, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3a991ee93a8420</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Security Engineer - Dallas - Associate</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Terraform, Git, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f0853676829ed4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cushman &amp; Wakefield</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Creve Coeur, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Git, Databricks, Tableau, Power BI, Python, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b21e6d09fdd6f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b5b2dd5e50c4ad3</t>
         </is>
       </c>
     </row>
